--- a/data/excel/Administration_AvenueManagement_RegisterStaff.xlsx
+++ b/data/excel/Administration_AvenueManagement_RegisterStaff.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A97B9C8-5C24-4D1A-B676-2617371627D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA77C5AF-4412-4A9B-98DF-1811596AA1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -55,15 +56,6 @@
     <t>qlabs12345</t>
   </si>
   <si>
-    <t>Verify Corporate Profiling</t>
-  </si>
-  <si>
-    <t>Piyush_QL</t>
-  </si>
-  <si>
-    <t>Password@123456</t>
-  </si>
-  <si>
     <t>Branch</t>
   </si>
   <si>
@@ -79,9 +71,6 @@
     <t>EmployeeName</t>
   </si>
   <si>
-    <t>Shubham Natkar</t>
-  </si>
-  <si>
     <t>PhoneCountry</t>
   </si>
   <si>
@@ -94,13 +83,28 @@
     <t>Email</t>
   </si>
   <si>
-    <t>test@quadlabs.com</t>
-  </si>
-  <si>
     <t>LoginName</t>
   </si>
   <si>
-    <t>ShubhamNatkar</t>
+    <t>Piyush_ql</t>
+  </si>
+  <si>
+    <t>EE6B4B@E7</t>
+  </si>
+  <si>
+    <t>Verify Register Staff</t>
+  </si>
+  <si>
+    <t>Verify Search Staff</t>
+  </si>
+  <si>
+    <t>Bal  Krushna</t>
+  </si>
+  <si>
+    <t>BalKrushna1</t>
+  </si>
+  <si>
+    <t>test7@quadlabs.com</t>
   </si>
 </sst>
 </file>
@@ -189,16 +193,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -521,26 +528,26 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -548,7 +555,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -559,29 +566,29 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>22</v>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
       </c>
       <c r="L2">
-        <v>8877994455</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>24</v>
+        <v>9874693213</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="N2" t="s">
         <v>26</v>
@@ -589,28 +596,102 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"at,qlabs12345"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>"Piyush_QL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>"Password@123456"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{A0830E6C-04B6-4FA6-B332-F855F02E7935}">
       <formula1>"Delhi travels,laxmi travel,QA Branch,QLABS Agency"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{84DF3301-8471-4E4D-9E45-CEFD36EADED4}">
       <formula1>"Administrator,Developer,Testing roles and right"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{E8CB61A2-BC1F-4982-A220-8F21A5BA1C49}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{B333026C-5DF4-41D3-A43B-2637F072E1C8}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{9BD070CA-18A1-4A41-8AEF-97C614E411C3}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G2" r:id="rId2" display="Piyush@321" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="M2" r:id="rId3" xr:uid="{02E51128-636F-42F8-8D72-F2D617EBCCE3}"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{02E51128-636F-42F8-8D72-F2D617EBCCE3}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{E912B0F7-0F49-4987-9E1D-FFE9715CD6CD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A03C740-78E8-4E4C-A126-BDB40B84E0D5}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{D096CE42-2D88-4C15-9E06-CF30F1CAB975}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{0D802A66-C428-40A6-8905-D7359AECC22E}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{52BBD323-9DDB-4E63-9254-87F15167F610}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{F6F82F51-9AA7-4B2C-B072-D6B018A7608E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/excel/Administration_AvenueManagement_RegisterStaff.xlsx
+++ b/data/excel/Administration_AvenueManagement_RegisterStaff.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA77C5AF-4412-4A9B-98DF-1811596AA1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D306BD-E954-4A35-9991-06B4350774E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,12 +86,6 @@
     <t>LoginName</t>
   </si>
   <si>
-    <t>Piyush_ql</t>
-  </si>
-  <si>
-    <t>EE6B4B@E7</t>
-  </si>
-  <si>
     <t>Verify Register Staff</t>
   </si>
   <si>
@@ -105,6 +99,12 @@
   </si>
   <si>
     <t>test7@quadlabs.com</t>
+  </si>
+  <si>
+    <t>k.gaurav</t>
+  </si>
+  <si>
+    <t>07DE6@EAB</t>
   </si>
 </sst>
 </file>
@@ -555,7 +555,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -567,10 +567,10 @@
         <v>10</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
@@ -579,7 +579,7 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
@@ -588,10 +588,10 @@
         <v>9874693213</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -602,19 +602,19 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{84DF3301-8471-4E4D-9E45-CEFD36EADED4}">
       <formula1>"Administrator,Developer,Testing roles and right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{E8CB61A2-BC1F-4982-A220-8F21A5BA1C49}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{323EEBD8-C2CE-4342-83DA-F202BF2D3B2C}">
       <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{B333026C-5DF4-41D3-A43B-2637F072E1C8}">
       <formula1>"at,qlabs12345,merg123456"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{9BD070CA-18A1-4A41-8AEF-97C614E411C3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{76A9B4FE-3613-42EF-9E43-8A7F58E2A118}">
       <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1" xr:uid="{02E51128-636F-42F8-8D72-F2D617EBCCE3}"/>
-    <hyperlink ref="G2" r:id="rId2" xr:uid="{E912B0F7-0F49-4987-9E1D-FFE9715CD6CD}"/>
+    <hyperlink ref="G2" r:id="rId2" display="EE6B4B@E7" xr:uid="{21955F26-86AF-4666-AD3F-6023954D81BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
@@ -654,12 +654,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -671,10 +671,10 @@
         <v>10</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -690,7 +690,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{F6F82F51-9AA7-4B2C-B072-D6B018A7608E}"/>
+    <hyperlink ref="G2" r:id="rId1" display="EE6B4B@E7" xr:uid="{F6F82F51-9AA7-4B2C-B072-D6B018A7608E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/excel/Administration_AvenueManagement_RegisterStaff.xlsx
+++ b/data/excel/Administration_AvenueManagement_RegisterStaff.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D306BD-E954-4A35-9991-06B4350774E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFE3233-6106-4970-AC9D-18785C5ED49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
